--- a/events/Szeged_2009_WC/Szeged_2009_WC_Results.xlsx
+++ b/events/Szeged_2009_WC/Szeged_2009_WC_Results.xlsx
@@ -3377,11 +3377,6 @@
           <t>04:22.811</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>64492</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5674,11 +5669,6 @@
           <t>03:43.171</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -22298,11 +22288,6 @@
           <t>01:58.501</t>
         </is>
       </c>
-      <c r="R349" t="inlineStr">
-        <is>
-          <t>64492</t>
-        </is>
-      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -26558,11 +26543,6 @@
           <t>01:35.348</t>
         </is>
       </c>
-      <c r="S418" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -31500,11 +31480,6 @@
           <t>04:20.911</t>
         </is>
       </c>
-      <c r="R497" t="inlineStr">
-        <is>
-          <t>64492</t>
-        </is>
-      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -33635,11 +33610,6 @@
           <t>03:31.229</t>
         </is>
       </c>
-      <c r="S531" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -46228,11 +46198,6 @@
           <t>04:33.902</t>
         </is>
       </c>
-      <c r="R732" t="inlineStr">
-        <is>
-          <t>64492</t>
-        </is>
-      </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
@@ -46888,11 +46853,6 @@
           <t>03:42.153</t>
         </is>
       </c>
-      <c r="S742" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
@@ -52820,11 +52780,6 @@
           <t>01:57.306</t>
         </is>
       </c>
-      <c r="R835" t="inlineStr">
-        <is>
-          <t>64492</t>
-        </is>
-      </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
@@ -56284,11 +56239,6 @@
           <t>01:35.520</t>
         </is>
       </c>
-      <c r="S891" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
@@ -66099,11 +66049,6 @@
           <t>02:02.662</t>
         </is>
       </c>
-      <c r="R1043" t="inlineStr">
-        <is>
-          <t>64492</t>
-        </is>
-      </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
@@ -67170,11 +67115,6 @@
       <c r="P1060" t="inlineStr">
         <is>
           <t>01:34.989</t>
-        </is>
-      </c>
-      <c r="S1060" t="inlineStr">
-        <is>
-          <t>51822</t>
         </is>
       </c>
     </row>
@@ -71816,7 +71756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D112"/>
+  <dimension ref="A1:D110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72020,83 +71960,83 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>51822</t>
+          <t>52150</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Scotty</t>
+          <t>Jo</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BICKNELL</t>
+          <t>BRIGDEN-JONES</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>52150</t>
+          <t>42447</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Jo</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BRIGDEN-JONES</t>
+          <t>BRYANT</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>42447</t>
+          <t>142729</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Jennifer</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BRYANT</t>
+          <t>BURKE</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>142729</t>
+          <t>36282</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Jennifer</t>
+          <t>Lisa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BURKE</t>
+          <t>CARRINGTON</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -72108,83 +72048,83 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>36282</t>
+          <t>36405</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lisa</t>
+          <t>Miguel Angel</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CARRINGTON</t>
+          <t>CASTANEDA CASTILLO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>36405</t>
+          <t>35813</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Miguel Angel</t>
+          <t>Rachel</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CASTANEDA CASTILLO</t>
+          <t>CAWTHORN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>35813</t>
+          <t>46354</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Rachel</t>
+          <t>Iurii</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CAWTHORN</t>
+          <t>CHEBAN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>46354</t>
+          <t>47495</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Iurii</t>
+          <t>Iosif</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CHEBAN</t>
+          <t>CHIRILA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -72196,61 +72136,61 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>47495</t>
+          <t>50186</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Iosif</t>
+          <t>Stefania</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CHIRILA</t>
+          <t>CICALI</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>50186</t>
+          <t>45846</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Stefania</t>
+          <t>Jacob</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CICALI</t>
+          <t>CLEAR</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>45846</t>
+          <t>42449</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jacob</t>
+          <t>Ryan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLEAR</t>
+          <t>COCHRANE</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -72262,17 +72202,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>42449</t>
+          <t>36399</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ryan</t>
+          <t>Everardo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>COCHRANE</t>
+          <t>CRISTOBAL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -72284,61 +72224,61 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>36399</t>
+          <t>53126</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Everardo</t>
+          <t>Tamara</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CRISTOBAL</t>
+          <t>CSIPES</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>53126</t>
+          <t>46717</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tamara</t>
+          <t>Andreas</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CSIPES</t>
+          <t>DIAMANTIS</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>46717</t>
+          <t>41545</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Andreas</t>
+          <t>Rudolf</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DIAMANTIS</t>
+          <t>DOMBI</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -72350,17 +72290,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>41545</t>
+          <t>47253</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Rudolf</t>
+          <t>Liviu Alexandru</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DOMBI</t>
+          <t>DUMITRESCU LAZAR</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -72372,61 +72312,61 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>47253</t>
+          <t>47434</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Liviu Alexandru</t>
+          <t>Krisztina</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DUMITRESCU LAZAR</t>
+          <t>FAZEKAS-ZUR</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>47434</t>
+          <t>42128</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Krisztina</t>
+          <t>Osbaldo</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>FAZEKAS-ZUR</t>
+          <t>FUENTES</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>42128</t>
+          <t>35927</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Osbaldo</t>
+          <t>Pawel</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FUENTES</t>
+          <t>FLORCZAK</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -72438,17 +72378,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>35927</t>
+          <t>125841</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pawel</t>
+          <t>Laszlo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FLORCZAK</t>
+          <t>FOLTAN</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -72460,61 +72400,61 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>125841</t>
+          <t>42453</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Laszlo</t>
+          <t>Emilie</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FOLTAN</t>
+          <t>FOURNEL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>42453</t>
+          <t>75776</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Emilie</t>
+          <t>Matthew</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FOURNEL</t>
+          <t>GOBLE</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>75776</t>
+          <t>35705</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Matthew</t>
+          <t>Marcus</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>GOBLE</t>
+          <t>GROSS</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -72526,17 +72466,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>35705</t>
+          <t>35876</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Marcus</t>
+          <t>Marcin</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>GROSS</t>
+          <t>GRZYBOWSKI</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -72548,61 +72488,61 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>35876</t>
+          <t>36670</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Marcin</t>
+          <t>Verena</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GRZYBOWSKI</t>
+          <t>HANTL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>64492</t>
+          <t>36391</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Thomas</t>
+          <t>Bridgitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>HALL</t>
+          <t>HARTLEY</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>36670</t>
+          <t>36283</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Verena</t>
+          <t>Teneale</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>HANTL</t>
+          <t>HATTON</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -72614,105 +72554,105 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>36391</t>
+          <t>66400</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Bridgitte</t>
+          <t>Asep</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HARTLEY</t>
+          <t>HIDAYAT</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>36283</t>
+          <t>35708</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Teneale</t>
+          <t>Martin</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>HATTON</t>
+          <t>HOLLSTEIN</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>66400</t>
+          <t>52174</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Asep</t>
+          <t>Jieyi</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>HIDAYAT</t>
+          <t>HUANG</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>35708</t>
+          <t>47433</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Martin</t>
+          <t>Natasa</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HOLLSTEIN</t>
+          <t>DOUCHEV-JANIC</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>52174</t>
+          <t>47633</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Jieyi</t>
+          <t>Karin</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>HUANG</t>
+          <t>JOHANSSON</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -72724,61 +72664,61 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>47433</t>
+          <t>35874</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Natasa</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DOUCHEV-JANIC</t>
+          <t>KACZOR</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>47633</t>
+          <t>46375</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Karin</t>
+          <t>Denys</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>JOHANSSON</t>
+          <t>KAMERYLOV</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>35874</t>
+          <t>41546</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tomasz</t>
+          <t>Zoltan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>KACZOR</t>
+          <t>KAMMERER</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -72790,17 +72730,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>46375</t>
+          <t>46122</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Denys</t>
+          <t>Miroslav</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>KAMERYLOV</t>
+          <t>KIRCHEV</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -72812,39 +72752,39 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>41546</t>
+          <t>41540</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Zoltan</t>
+          <t>Danuta</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>KAMMERER</t>
+          <t>KOZAK</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>46122</t>
+          <t>35937</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Miroslav</t>
+          <t>Arkadiusz</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>KIRCHEV</t>
+          <t>KRAJEWSKI</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -72856,39 +72796,39 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>41540</t>
+          <t>53108</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Danuta</t>
+          <t>Attila</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>KOZAK</t>
+          <t>KUGLER</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>35937</t>
+          <t>35871</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Arkadiusz</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>KRAJEWSKI</t>
+          <t>KULETA</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -72900,17 +72840,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>53108</t>
+          <t>41544</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Attila</t>
+          <t>Roland</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>KUGLER</t>
+          <t>KOKENY</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -72922,17 +72862,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>35871</t>
+          <t>61246</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Pierre-Luc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>KULETA</t>
+          <t>LALIBERTE</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -72944,39 +72884,39 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>41544</t>
+          <t>35562</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Roland</t>
+          <t>Ana-Roxana</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>KOKENY</t>
+          <t>LEHACI</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>61246</t>
+          <t>35719</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Pierre-Luc</t>
+          <t>Erik</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LALIBERTE</t>
+          <t>LEUE</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -72988,61 +72928,61 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>35562</t>
+          <t>99871</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ana-Roxana</t>
+          <t>Marko</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LEHACI</t>
+          <t>LIPOVAC</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>35719</t>
+          <t>42461</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Erik</t>
+          <t>Una Helen Bean</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LEUE</t>
+          <t>LOUNDER</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>99871</t>
+          <t>36389</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Marko</t>
+          <t>Greg</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>LIPOVAC</t>
+          <t>LOUW</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -73054,127 +72994,127 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>42461</t>
+          <t>35928</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Una Helen Bean</t>
+          <t>Rafal</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LOUNDER</t>
+          <t>MARON</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>36389</t>
+          <t>36224</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Greg</t>
+          <t>Hayleigh-Jayne</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>LOUW</t>
+          <t>MASON</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>35928</t>
+          <t>47432</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Rafal</t>
+          <t>Erika</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MARON</t>
+          <t>MEDVECZKY</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>36224</t>
+          <t>47673</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Hayleigh-Jayne</t>
+          <t>Vadim</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MASON</t>
+          <t>MENKOV</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>47432</t>
+          <t>47252</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Erika</t>
+          <t>Victor</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MEDVECZKY</t>
+          <t>MIHALACHI</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>47673</t>
+          <t>47427</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Vadim</t>
+          <t>Robert</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MENKOV</t>
+          <t>MIKE</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -73186,17 +73126,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>47252</t>
+          <t>47261</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Victor</t>
+          <t>Ionut</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MIHALACHI</t>
+          <t>MITREA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -73208,17 +73148,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>47427</t>
+          <t>35721</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Robert</t>
+          <t>Paul</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MIKE</t>
+          <t>MITTELSTEDT</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -73230,39 +73170,39 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>47261</t>
+          <t>42187</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Ionut</t>
+          <t>Nikolina</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MITREA</t>
+          <t>MOLDOVAN</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>35721</t>
+          <t>47423</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Paul</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MITTELSTEDT</t>
+          <t>MOLNAR</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -73274,61 +73214,61 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>42187</t>
+          <t>42465</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Nikolina</t>
+          <t>Angus</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MOLDOVAN</t>
+          <t>MORTIMER</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>47423</t>
+          <t>36562</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Norma</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MOLNAR</t>
+          <t>MURABITO</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>42465</t>
+          <t>47425</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Angus</t>
+          <t>Peter</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MORTIMER</t>
+          <t>NAGY</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -73340,17 +73280,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>36562</t>
+          <t>35557</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Norma</t>
+          <t>Karolina</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MURABITO</t>
+          <t>NAJA</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -73362,17 +73302,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>47425</t>
+          <t>65873</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Peter</t>
+          <t>Traian</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NAGY</t>
+          <t>NEAGU</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -73384,61 +73324,61 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>35557</t>
+          <t>152403</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Karolina</t>
+          <t>Viktor</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NAJA</t>
+          <t>NEDASHKOVSKYY</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>65873</t>
+          <t>45837</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Traian</t>
+          <t>Alana</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NEAGU</t>
+          <t>NICHOLLS</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>152403</t>
+          <t>42181</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Viktor</t>
+          <t>Marko</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NEDASHKOVSKYY</t>
+          <t>NOVAKOVIC</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -73450,83 +73390,83 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>45837</t>
+          <t>42466</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Alana</t>
+          <t>Mark William</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NICHOLLS</t>
+          <t>OLDERSHAW</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>42181</t>
+          <t>42467</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Marko</t>
+          <t>Genevieve Wendy Susan</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NOVAKOVIC</t>
+          <t>ORTON</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>42466</t>
+          <t>51871</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Mark William</t>
+          <t>Sofia</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>OLDERSHAW</t>
+          <t>PALDANIUS</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>42467</t>
+          <t>73720</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Genevieve Wendy Susan</t>
+          <t>Melinda</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ORTON</t>
+          <t>HILDENBRAND-PATYI</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -73538,83 +73478,83 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>51871</t>
+          <t>105242</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Sofia</t>
+          <t>Milos</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PALDANIUS</t>
+          <t>PETROVIC</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>73720</t>
+          <t>45847</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Melinda</t>
+          <t>Jesse</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>HILDENBRAND-PATYI</t>
+          <t>PHILLIPS</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>105242</t>
+          <t>36313</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Milos</t>
+          <t>Spela</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PETROVIC</t>
+          <t>PONOMARENKO JANIC</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>45847</t>
+          <t>35724</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Jesse</t>
+          <t>Ronald</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>PHILLIPS</t>
+          <t>RAUHE</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -73626,39 +73566,39 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>36313</t>
+          <t>42468</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Spela</t>
+          <t>Brady Daniel Heim</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PONOMARENKO JANIC</t>
+          <t>REARDON</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>35724</t>
+          <t>35725</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Ronald</t>
+          <t>Erik</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>RAUHE</t>
+          <t>REBSTOCK</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -73670,17 +73610,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>42468</t>
+          <t>47436</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Brady Daniel Heim</t>
+          <t>Pal</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>REARDON</t>
+          <t>SARUDI</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -73692,105 +73632,105 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>35725</t>
+          <t>35561</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Erik</t>
+          <t>Yvonne</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>REBSTOCK</t>
+          <t>SCHURING</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>47436</t>
+          <t>35560</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Pal</t>
+          <t>Viktoria</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SARUDI</t>
+          <t>SCHWARZ</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>35561</t>
+          <t>35858</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Yvonne</t>
+          <t>Piotr</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SCHURING</t>
+          <t>SIEMIONOWSKI</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>35560</t>
+          <t>45844</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Viktoria</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SCHWARZ</t>
+          <t>SMITH</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>35858</t>
+          <t>45793</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Piotr</t>
+          <t>Murray</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SIEMIONOWSKI</t>
+          <t>STEWART</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -73802,39 +73742,39 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>45844</t>
+          <t>41542</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Gabriella</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>SMITH</t>
+          <t>SZABO</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>45793</t>
+          <t>53107</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Murray</t>
+          <t>Tamas</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>STEWART</t>
+          <t>SZALAI</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -73846,39 +73786,39 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>41542</t>
+          <t>98550</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Gabriella</t>
+          <t>Matyas</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SZABO</t>
+          <t>SAFRAN</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>53107</t>
+          <t>44441</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tamas</t>
+          <t>Juraj</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SZALAI</t>
+          <t>TARR</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -73890,17 +73830,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>98550</t>
+          <t>66401</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Matyas</t>
+          <t>Anwar</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SAFRAN</t>
+          <t>TARRA</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -73912,17 +73852,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>44441</t>
+          <t>42184</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Juraj</t>
+          <t>Marko</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>TARR</t>
+          <t>TOMICEVIC</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -73934,39 +73874,39 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>66401</t>
+          <t>45512</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Anwar</t>
+          <t>Dzsenifer</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>TARRA</t>
+          <t>TOTH</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>42184</t>
+          <t>41549</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Marko</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>TOMICEVIC</t>
+          <t>TOTH</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -73978,17 +73918,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>45512</t>
+          <t>47435</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Dzsenifer</t>
+          <t>Ninetta</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>TOTH</t>
+          <t>VAD</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -74000,17 +73940,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>41549</t>
+          <t>41550</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Attila</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>TOTH</t>
+          <t>VAJDA</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -74022,39 +73962,39 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>47435</t>
+          <t>42285</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Ninetta</t>
+          <t>Adam</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>VAD</t>
+          <t>VAN KOEVERDEN</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>41550</t>
+          <t>47429</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Attila</t>
+          <t>David</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>VAJDA</t>
+          <t>VARGA</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -74066,17 +74006,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>42285</t>
+          <t>46387</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Adam</t>
+          <t>Vitaliy</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>VAN KOEVERDEN</t>
+          <t>VERHELES</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -74088,17 +74028,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>47429</t>
+          <t>45725</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Erik</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>VARGA</t>
+          <t>VLCEK</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -74110,61 +74050,61 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>46387</t>
+          <t>35730</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Vitaliy</t>
+          <t>Sabine</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>VERHELES</t>
+          <t>VOLZ</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>45725</t>
+          <t>36222</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Erik</t>
+          <t>Jessica</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>VLCEK</t>
+          <t>WALKER</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>35730</t>
+          <t>42209</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Sabine</t>
+          <t>Bernadette</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>VOLZ</t>
+          <t>WALLACE</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -74176,17 +74116,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>36222</t>
+          <t>69210</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Jessica</t>
+          <t>Emily</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>WALKER</t>
+          <t>WRIGHT</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -74198,86 +74138,42 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>42209</t>
+          <t>35737</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Bernadette</t>
+          <t>Tomasz</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>WALLACE</t>
+          <t>WYLENZEK</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>69210</t>
+          <t>42179</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Emily</t>
+          <t>Milenko</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>WRIGHT</t>
+          <t>ZORIC</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>35737</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Tomasz</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>WYLENZEK</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>42179</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Milenko</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>ZORIC</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
         <is>
           <t>M</t>
         </is>

--- a/events/Szeged_2009_WC/Szeged_2009_WC_Results.xlsx
+++ b/events/Szeged_2009_WC/Szeged_2009_WC_Results.xlsx
@@ -602,6 +602,11 @@
           <t>03:51.701</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>36567</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2262,6 +2267,11 @@
           <t>03:50.148</t>
         </is>
       </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -9058,6 +9068,11 @@
           <t>42423</t>
         </is>
       </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>36446</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -9188,6 +9203,11 @@
           <t>42179</t>
         </is>
       </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>130129</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -9318,6 +9338,11 @@
           <t>53107</t>
         </is>
       </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>41548</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -10727,6 +10752,11 @@
           <t>00:39.914</t>
         </is>
       </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -18508,6 +18538,11 @@
           <t>63480</t>
         </is>
       </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>36446</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -19093,6 +19128,11 @@
           <t>00:34.270</t>
         </is>
       </c>
+      <c r="R297" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -20328,6 +20368,11 @@
           <t>01:45.508</t>
         </is>
       </c>
+      <c r="R317" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -25738,6 +25783,11 @@
           <t>63480</t>
         </is>
       </c>
+      <c r="S405" t="inlineStr">
+        <is>
+          <t>36446</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -25863,6 +25913,11 @@
           <t>42179</t>
         </is>
       </c>
+      <c r="S407" t="inlineStr">
+        <is>
+          <t>130129</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -25923,6 +25978,11 @@
           <t>01:43.835</t>
         </is>
       </c>
+      <c r="R408" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -29945,6 +30005,11 @@
           <t>03:50.567</t>
         </is>
       </c>
+      <c r="R472" t="inlineStr">
+        <is>
+          <t>36567</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
@@ -30930,6 +30995,11 @@
           <t>03:45.621</t>
         </is>
       </c>
+      <c r="R488" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
@@ -35638,6 +35708,11 @@
           <t>42179</t>
         </is>
       </c>
+      <c r="S564" t="inlineStr">
+        <is>
+          <t>130129</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
@@ -35955,6 +36030,11 @@
           <t>42423</t>
         </is>
       </c>
+      <c r="T569" t="inlineStr">
+        <is>
+          <t>36446</t>
+        </is>
+      </c>
       <c r="X569" t="inlineStr">
         <is>
           <t>DSQ</t>
@@ -37200,6 +37280,11 @@
           <t>00:40.585</t>
         </is>
       </c>
+      <c r="R589" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -42272,6 +42357,11 @@
           <t>00:34.946</t>
         </is>
       </c>
+      <c r="R671" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="672">
       <c r="A672" t="inlineStr">
@@ -45429,6 +45519,11 @@
           <t>03:47.625</t>
         </is>
       </c>
+      <c r="R720" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="721">
       <c r="A721" t="inlineStr">
@@ -45491,6 +45586,11 @@
           <t>03:48.243</t>
         </is>
       </c>
+      <c r="R721" t="inlineStr">
+        <is>
+          <t>36567</t>
+        </is>
+      </c>
     </row>
     <row r="722">
       <c r="A722" t="inlineStr">
@@ -48294,6 +48394,11 @@
           <t>53107</t>
         </is>
       </c>
+      <c r="U764" t="inlineStr">
+        <is>
+          <t>41548</t>
+        </is>
+      </c>
     </row>
     <row r="765">
       <c r="A765" t="inlineStr">
@@ -48778,6 +48883,11 @@
           <t>42179</t>
         </is>
       </c>
+      <c r="S771" t="inlineStr">
+        <is>
+          <t>130129</t>
+        </is>
+      </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
@@ -49185,6 +49295,11 @@
           <t>47436</t>
         </is>
       </c>
+      <c r="U777" t="inlineStr">
+        <is>
+          <t>49667</t>
+        </is>
+      </c>
     </row>
     <row r="778">
       <c r="A778" t="inlineStr">
@@ -51488,6 +51603,11 @@
           <t>01:43.704</t>
         </is>
       </c>
+      <c r="R814" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
@@ -55499,6 +55619,11 @@
           <t>63480</t>
         </is>
       </c>
+      <c r="S879" t="inlineStr">
+        <is>
+          <t>36446</t>
+        </is>
+      </c>
     </row>
     <row r="880">
       <c r="A880" t="inlineStr">
@@ -56369,6 +56494,11 @@
           <t>42179</t>
         </is>
       </c>
+      <c r="S893" t="inlineStr">
+        <is>
+          <t>130129</t>
+        </is>
+      </c>
     </row>
     <row r="894">
       <c r="A894" t="inlineStr">
@@ -58193,6 +58323,11 @@
           <t>00:38.462</t>
         </is>
       </c>
+      <c r="R922" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="923">
       <c r="A923" t="inlineStr">
@@ -63641,6 +63776,11 @@
           <t>63480</t>
         </is>
       </c>
+      <c r="S1006" t="inlineStr">
+        <is>
+          <t>36446</t>
+        </is>
+      </c>
     </row>
     <row r="1007">
       <c r="A1007" t="inlineStr">
@@ -68608,6 +68748,11 @@
           <t>01:44.660</t>
         </is>
       </c>
+      <c r="R1083" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="1084">
       <c r="A1084" t="inlineStr">
@@ -70546,6 +70691,11 @@
       <c r="R1113" t="inlineStr">
         <is>
           <t>63480</t>
+        </is>
+      </c>
+      <c r="S1113" t="inlineStr">
+        <is>
+          <t>36446</t>
         </is>
       </c>
     </row>
@@ -71756,7 +71906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D110"/>
+  <dimension ref="A1:D117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74179,6 +74329,160 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>36446</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Alberto</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>RICCHETTI</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>36567</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Maximilian</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>BENASSI</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>41548</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>PAUMAN</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Kenny</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>WALLACE</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Timothy</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>HORNSBY</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>49667</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Tamas</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>KISS</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>130129</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Milan</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>GAJDOBRANSKI</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Szeged_2009_WC/Szeged_2009_WC_Results.xlsx
+++ b/events/Szeged_2009_WC/Szeged_2009_WC_Results.xlsx
@@ -3387,6 +3387,11 @@
           <t>04:22.811</t>
         </is>
       </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>64492</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5679,6 +5684,11 @@
           <t>03:43.171</t>
         </is>
       </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>51822</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -22333,6 +22343,11 @@
           <t>01:58.501</t>
         </is>
       </c>
+      <c r="R349" t="inlineStr">
+        <is>
+          <t>64492</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -26603,6 +26618,11 @@
           <t>01:35.348</t>
         </is>
       </c>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>51822</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -31550,6 +31570,11 @@
           <t>04:20.911</t>
         </is>
       </c>
+      <c r="R497" t="inlineStr">
+        <is>
+          <t>64492</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -33680,6 +33705,11 @@
           <t>03:31.229</t>
         </is>
       </c>
+      <c r="S531" t="inlineStr">
+        <is>
+          <t>51822</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -46298,6 +46328,11 @@
           <t>04:33.902</t>
         </is>
       </c>
+      <c r="R732" t="inlineStr">
+        <is>
+          <t>64492</t>
+        </is>
+      </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
@@ -46953,6 +46988,11 @@
           <t>03:42.153</t>
         </is>
       </c>
+      <c r="S742" t="inlineStr">
+        <is>
+          <t>51822</t>
+        </is>
+      </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
@@ -52900,6 +52940,11 @@
           <t>01:57.306</t>
         </is>
       </c>
+      <c r="R835" t="inlineStr">
+        <is>
+          <t>64492</t>
+        </is>
+      </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
@@ -56364,6 +56409,11 @@
           <t>01:35.520</t>
         </is>
       </c>
+      <c r="S891" t="inlineStr">
+        <is>
+          <t>51822</t>
+        </is>
+      </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
@@ -66189,6 +66239,11 @@
           <t>02:02.662</t>
         </is>
       </c>
+      <c r="R1043" t="inlineStr">
+        <is>
+          <t>64492</t>
+        </is>
+      </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
@@ -67255,6 +67310,11 @@
       <c r="P1060" t="inlineStr">
         <is>
           <t>01:34.989</t>
+        </is>
+      </c>
+      <c r="S1060" t="inlineStr">
+        <is>
+          <t>51822</t>
         </is>
       </c>
     </row>
@@ -71906,7 +71966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D117"/>
+  <dimension ref="A1:D119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74483,6 +74543,50 @@
         </is>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>51822</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Scotty</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>BICKNELL</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>64492</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Thomas</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>HALL</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Szeged_2009_WC/Szeged_2009_WC_Results.xlsx
+++ b/events/Szeged_2009_WC/Szeged_2009_WC_Results.xlsx
@@ -3387,11 +3387,6 @@
           <t>04:22.811</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
-        <is>
-          <t>64492</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5684,11 +5679,6 @@
           <t>03:43.171</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -22343,11 +22333,6 @@
           <t>01:58.501</t>
         </is>
       </c>
-      <c r="R349" t="inlineStr">
-        <is>
-          <t>64492</t>
-        </is>
-      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -26618,11 +26603,6 @@
           <t>01:35.348</t>
         </is>
       </c>
-      <c r="S418" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -31570,11 +31550,6 @@
           <t>04:20.911</t>
         </is>
       </c>
-      <c r="R497" t="inlineStr">
-        <is>
-          <t>64492</t>
-        </is>
-      </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
@@ -33705,11 +33680,6 @@
           <t>03:31.229</t>
         </is>
       </c>
-      <c r="S531" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
@@ -46328,11 +46298,6 @@
           <t>04:33.902</t>
         </is>
       </c>
-      <c r="R732" t="inlineStr">
-        <is>
-          <t>64492</t>
-        </is>
-      </c>
     </row>
     <row r="733">
       <c r="A733" t="inlineStr">
@@ -46988,11 +46953,6 @@
           <t>03:42.153</t>
         </is>
       </c>
-      <c r="S742" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="743">
       <c r="A743" t="inlineStr">
@@ -52940,11 +52900,6 @@
           <t>01:57.306</t>
         </is>
       </c>
-      <c r="R835" t="inlineStr">
-        <is>
-          <t>64492</t>
-        </is>
-      </c>
     </row>
     <row r="836">
       <c r="A836" t="inlineStr">
@@ -56409,11 +56364,6 @@
           <t>01:35.520</t>
         </is>
       </c>
-      <c r="S891" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
     </row>
     <row r="892">
       <c r="A892" t="inlineStr">
@@ -66239,11 +66189,6 @@
           <t>02:02.662</t>
         </is>
       </c>
-      <c r="R1043" t="inlineStr">
-        <is>
-          <t>64492</t>
-        </is>
-      </c>
     </row>
     <row r="1044">
       <c r="A1044" t="inlineStr">
@@ -67310,11 +67255,6 @@
       <c r="P1060" t="inlineStr">
         <is>
           <t>01:34.989</t>
-        </is>
-      </c>
-      <c r="S1060" t="inlineStr">
-        <is>
-          <t>51822</t>
         </is>
       </c>
     </row>
@@ -71966,7 +71906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D119"/>
+  <dimension ref="A1:D117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74543,50 +74483,6 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>51822</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Scotty</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>BICKNELL</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>64492</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Thomas</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>HALL</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Szeged_2009_WC/Szeged_2009_WC_Results.xlsx
+++ b/events/Szeged_2009_WC/Szeged_2009_WC_Results.xlsx
@@ -1587,6 +1587,11 @@
           <t>03:58.226</t>
         </is>
       </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>42126</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2517,6 +2522,11 @@
           <t>03:56.052</t>
         </is>
       </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -5864,6 +5874,11 @@
           <t>03:47.425</t>
         </is>
       </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>47627</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -9722,6 +9737,11 @@
       <c r="N147" t="n">
         <v>7</v>
       </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>42126</t>
+        </is>
+      </c>
       <c r="U147" t="inlineStr">
         <is>
           <t>42128</t>
@@ -15858,6 +15878,11 @@
           <t>00:37.417</t>
         </is>
       </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>47627</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -18813,6 +18838,11 @@
           <t>42128</t>
         </is>
       </c>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>42126</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -21473,6 +21503,11 @@
           <t>01:49.277</t>
         </is>
       </c>
+      <c r="R335" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -26908,6 +26943,11 @@
           <t>01:40.064</t>
         </is>
       </c>
+      <c r="R423" t="inlineStr">
+        <is>
+          <t>42126</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -26968,6 +27008,11 @@
           <t>01:36.312</t>
         </is>
       </c>
+      <c r="R424" t="inlineStr">
+        <is>
+          <t>47627</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -30875,6 +30920,11 @@
           <t>04:02.908</t>
         </is>
       </c>
+      <c r="R486" t="inlineStr">
+        <is>
+          <t>42126</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
@@ -31240,6 +31290,11 @@
           <t>03:50.217</t>
         </is>
       </c>
+      <c r="R492" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -33305,6 +33360,11 @@
           <t>03:32.565</t>
         </is>
       </c>
+      <c r="R525" t="inlineStr">
+        <is>
+          <t>47627</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
@@ -40672,6 +40732,11 @@
           <t>00:37.382</t>
         </is>
       </c>
+      <c r="R644" t="inlineStr">
+        <is>
+          <t>47627</t>
+        </is>
+      </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
@@ -42497,6 +42562,11 @@
           <t>42128</t>
         </is>
       </c>
+      <c r="S673" t="inlineStr">
+        <is>
+          <t>42126</t>
+        </is>
+      </c>
     </row>
     <row r="674">
       <c r="A674" t="inlineStr">
@@ -43376,6 +43446,11 @@
           <t>04:09.718</t>
         </is>
       </c>
+      <c r="R687" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
@@ -44636,6 +44711,11 @@
           <t>03:56.773</t>
         </is>
       </c>
+      <c r="R707" t="inlineStr">
+        <is>
+          <t>47627</t>
+        </is>
+      </c>
     </row>
     <row r="708">
       <c r="A708" t="inlineStr">
@@ -51298,6 +51378,11 @@
           <t>01:47.668</t>
         </is>
       </c>
+      <c r="R809" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
@@ -55049,6 +55134,11 @@
           <t>01:34.016</t>
         </is>
       </c>
+      <c r="R870" t="inlineStr">
+        <is>
+          <t>47627</t>
+        </is>
+      </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
@@ -62096,6 +62186,11 @@
           <t>00:36.062</t>
         </is>
       </c>
+      <c r="R981" t="inlineStr">
+        <is>
+          <t>47627</t>
+        </is>
+      </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
@@ -65123,6 +65218,11 @@
           <t>01:47.913</t>
         </is>
       </c>
+      <c r="R1026" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
     </row>
     <row r="1027">
       <c r="A1027" t="inlineStr">
@@ -70495,6 +70595,11 @@
       <c r="P1110" t="inlineStr">
         <is>
           <t>01:38.117</t>
+        </is>
+      </c>
+      <c r="R1110" t="inlineStr">
+        <is>
+          <t>47627</t>
         </is>
       </c>
     </row>
@@ -71906,7 +72011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D117"/>
+  <dimension ref="A1:D120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74483,6 +74588,72 @@
         </is>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>42126</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Jesus</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>VALDES</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>36232</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Jonathon</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>BOYTON</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>47627</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Christian</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>SVAMQVIST</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Szeged_2009_WC/Szeged_2009_WC_Results.xlsx
+++ b/events/Szeged_2009_WC/Szeged_2009_WC_Results.xlsx
@@ -3947,6 +3947,11 @@
           <t>04:34.951</t>
         </is>
       </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -13351,6 +13356,11 @@
           <t>00:45.815</t>
         </is>
       </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -22928,6 +22938,11 @@
           <t>02:00.316</t>
         </is>
       </c>
+      <c r="R358" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -31970,6 +31985,11 @@
           <t>04:41.977</t>
         </is>
       </c>
+      <c r="R503" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
@@ -38697,6 +38717,11 @@
           <t>00:45.915</t>
         </is>
       </c>
+      <c r="R611" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
@@ -44081,6 +44106,11 @@
           <t>04:52.090</t>
         </is>
       </c>
+      <c r="R697" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="698">
       <c r="A698" t="inlineStr">
@@ -52925,6 +52955,11 @@
           <t>01:56.940</t>
         </is>
       </c>
+      <c r="R834" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="835">
       <c r="A835" t="inlineStr">
@@ -60628,6 +60663,11 @@
           <t>00:42.370</t>
         </is>
       </c>
+      <c r="R957" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="958">
       <c r="A958" t="inlineStr">
@@ -69362,6 +69402,11 @@
       <c r="P1091" t="inlineStr">
         <is>
           <t>01:59.129</t>
+        </is>
+      </c>
+      <c r="R1091" t="inlineStr">
+        <is>
+          <t>36633</t>
         </is>
       </c>
     </row>
@@ -72011,7 +72056,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D120"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74654,6 +74699,28 @@
         </is>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Nivalter</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Santos de Jesus</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
